--- a/vse-loti/339402485/spec-339402485.xlsx
+++ b/vse-loti/339402485/spec-339402485.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +61,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,19 +435,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,19 +503,63 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Комплект ирригационных трубок для системы абляции сердца Способ определения поставщика (подрядчика, исполнителя) Электронный аукцион Наименование электронной площадки в информационно-телекоммуникационной сети «Интернет» ЭТП ТЭК-Торг Адрес электронной площадки в информационно-телекоммуникационной сети «Интернет» http://www.tektorg.ru/ Размещение осуществляет Заказчик ФЕДЕРАЛЬНОЕ ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ НАУЧНОЕ УЧРЕЖДЕНИЕ "НАУЧНО-ИССЛЕДОВАТЕЛЬСКИЙ ИНСТИТУТ КОМПЛЕКСНЫХ ПРОБЛЕМ СЕРДЕЧНО-СОСУДИСТЫХ ЗАБОЛЕВАНИЙ" Контактная информация Организация, осуществляющая размещение ФЕДЕРАЛЬНОЕ ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ НАУЧНОЕ УЧРЕЖДЕНИЕ "НАУЧНО-ИССЛЕДОВАТЕЛЬСКИЙ ИНСТИТУТ КОМПЛЕКСНЫХ ПРОБЛЕМ СЕРДЕЧНО-СОСУДИСТЫХ ЗАБОЛЕВАНИЙ" Почтовый адрес Российская Федерация, 650002, Кемеровская область - Кузбасс обл, Кемерово г, имени академика Л.С. Барбараша б-р, СТР. 6 Место нахождения Российская Федерация, 650002, Кемеровская область - Кузбасс обл, Кемерово г, имени академика Л.С. Барбараша б-р, СТР. 6 Ответственное должностное лицо Зайцева Ольга Сергеевна Адрес электронной почты torginii@kemcardio.ru Номер контактного телефона 7-3842-345372 Факс Информация отсутствует Дополнительная информация Информация отсутствует Информация о процедуре закупки Дата и время окончания срока подачи заявок 02.09.2026 09:00 Дата проведения процедуры подачи предложений о цене контракта либо о сумме цен единиц товара, работы, услуги 02.09.2026 Дата подведения итогов определения поставщика (подрядчика, исполнителя) 04.09.2026 Условия контракта Начальная (максимальная) цена контракта 3547500.00 РОССИЙСКИЙ РУБЛЬ Информация о сроках исполнения контракта и источниках финансирования Дата начала исполнения контракта 17.09.2026 но не ранее даты заключения контракта Срок исполнения контракта 07.12.2027 Закупка за счет бюджетных средств Нет Закупка за счет собственных средств организации Да Финансовое обеспечение закупки Всего: Оплата за 2026 год Оплата за 2027 год Оплата за 2028 год Сумма на последующие годы 3547500.00 165000.00 3382500.00 0.00 0.00 Этапы исполнения контракта Контракт не разделен на этапы исполнения контракта Финансирование за счет внебюджетных средств Всего: Оплата за 2026 год Оплата за 2027 год Оплата за 2028 год Сумма на последующие годы 3547500.00 165000.00 3382500.00 0.00 0.00 Код видов расходов Код поступления Сумма контракта (в валюте контракта) Всего: на 2026 год на 2027 год на 2028 год Сумма на последующие годы 1 2 3 4 5 6 7 244 3547500.00 165000.00 3382500.00 0.00 0.00 Итого 165000.00 3382500.00 0.00 0.00 Идентификационный код закупки 261420501229042050100104735243250244 Место поставки товара, выполнения работы или оказания услуги Российская Федерация, обл. Кемеровская область - Кузбасс, г.о. Кемеровский, г. Кемерово, б-р имени академика Л.С. Барбараша, стр. 6, Предусмотрена возможность одностороннего отказа от исполнения контракта в соответствии со ст. 95 Закона № 44-ФЗ Да Объект закупки Наименование товара, работы, услуги Код позиции Тип позиции Единица измерения Цена за единицу Количество (объем работы, услуги) Стоимость позиции Комплект ирригационных трубок для системы абляции сердца Идентификатор: 221235221 32.50.13.110-00005862 Товар Штука 16500.00 215.00000000000 3547500.00 Характеристики товара, работы, услуги ( Комплект ирригационных трубок для системы абляции сердца ) Наименование характеристики Значение характеристики Единица измерения характеристики Инструкция по заполнению характеристики в заявке Обоснование включения дополнительной информации в сведения о товаре, работе, услуге Внутренний диаметр иглы 3.4 Миллиметр Значение характеристики не может изменяться участником закупки Высота капельницы ≥ 63 Миллиметр Участник закупки указывает в заявке конкретное значение характеристики Общая длина ≥ 3000 и ≤ 4100 Миллиметр Участник закупки указывает в заявке конкретное значение характеристики 1.Штекерный разъём Люэра наличие Значение характеристики не может изменяться участником закупки • 1.Разъём Люера необходим для фиксации в катетере. • 2.Поставляется в стерильной упаковке для соблюдения медицинских стандартов. • 3. Обеспечение совместимости с оборудованием, состоящим на балансе Заказчика. 2.Стерильность да Значение характеристики не может изменяться участником закупки • 1.Разъём Люера необходим для фиксации в катетере. • 2.Поставляется в стерильной упаковке для соблюдения медицинских стандартов. • 3. Обеспечение совместимости с оборудованием, состоящим на балансе Заказчика. 3.Совместимость трубки совместимы с ирригационным насосом SmartAblate Значение характеристики не может изменяться участником закупки • 1.Разъём Люера необходим для фиксации в катетере. • 2.Поставляется в стерильной упаковке для соблюдения медицинских стандартов. • 3. Обеспечение совместимости с оборудованием, состоящим на балансе Заказчика. Итого: 3547500.00 РОССИЙСКИЙ РУБЛЬ Преимущества и требования к участникам Преимущества Преимущество в соответствии с ч. 3 ст. 30 Закона № 44-ФЗ Требования к участникам 1 Единые требования к участникам закупок в соответствии с ч. 1 ст. 31 Закона № 44-ФЗ 2 Требования к участникам закупок в соответствии с ч. 1.1 ст. 31 Закона № 44-ФЗ 3 Требование об отсутствии в реестре недобросовестных поставщиков (подрядчиков, исполнителей) информации, включенной в такой реестр в связи отказом поставщика (подрядчика, исполнителя) от исполнения контракта по причине введения в отношении заказчика санкций и (или) мер ограничительного характера Применение национального режима по ст. 14 Закона № 44-ФЗ Основанием для установки указания запретов, ограничений закупок товаров, происходящих из иностранных государств, выполняемых работ, оказываемых услуг иностранными лицами, а также преимуществ в отношении товаров российского происхождения, а также товаров происходящих из стран ЕАЭС, выполняемых работ, оказываемых услуг российскими лицами, а также лицами, зарегистрированными в странах ЕАЭС, является Постановление Правительства Российской Федерации о мерах по предоставлению национального режима от 23.12.2024 № 1875. Объект закупки Вид требования Обоснование невозможности соблюдения запрета, ограничения 32.50.13.110</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>5862</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="3" t="n">
+        <v>605.17</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>726.2</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>3547500</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>605.17</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>726.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>0</v>
+      <c r="H3" s="5" t="n">
+        <v>3547500</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Источник: 852469524.doc</t>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>3547500</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Источник: 852469528.txt</t>
         </is>
       </c>
     </row>

--- a/vse-loti/339402485/spec-339402485.xlsx
+++ b/vse-loti/339402485/spec-339402485.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -66,10 +65,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -446,8 +445,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,25 +475,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (без НДС)</t>
+          <t>Стоимость (без НДС)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (с НДС)</t>
+          <t>Цена за т (без НДС)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Стоимость (без НДС)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -521,20 +508,10 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>605.17</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>726.2</v>
-      </c>
-      <c r="H2" s="3" t="n">
         <v>3547500</v>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>605.17</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>726.2</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -542,7 +519,7 @@
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="F3" s="5" t="n">
         <v>3547500</v>
       </c>
     </row>
@@ -552,7 +529,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="F4" s="5" t="n">
         <v>3547500</v>
       </c>
     </row>

--- a/vse-loti/339402485/spec-339402485.xlsx
+++ b/vse-loti/339402485/spec-339402485.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,14 +28,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,7 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
+        <fgColor rgb="FF305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,15 +74,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,20 +460,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>№</t>
@@ -455,35 +482,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Наименование позиции (⌀ + s, если указано)</t>
+          <t>Наименование позиции</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>D×s, мм (или характеристика)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Кол-во (исх.)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Масса, т (приведённая)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Цена за т (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -495,48 +527,89 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Комплект ирригационных трубок для системы абляции сердца Способ определения поставщика (подрядчика, исполнителя) Электронный аукцион Наименование электронной площадки в информационно-телекоммуникационной сети «Интернет» ЭТП ТЭК-Торг Адрес электронной площадки в информационно-телекоммуникационной сети «Интернет» http://www.tektorg.ru/ Размещение осуществляет Заказчик ФЕДЕРАЛЬНОЕ ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ НАУЧНОЕ УЧРЕЖДЕНИЕ "НАУЧНО-ИССЛЕДОВАТЕЛЬСКИЙ ИНСТИТУТ КОМПЛЕКСНЫХ ПРОБЛЕМ СЕРДЕЧНО-СОСУДИСТЫХ ЗАБОЛЕВАНИЙ" Контактная информация Организация, осуществляющая размещение ФЕДЕРАЛЬНОЕ ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ НАУЧНОЕ УЧРЕЖДЕНИЕ "НАУЧНО-ИССЛЕДОВАТЕЛЬСКИЙ ИНСТИТУТ КОМПЛЕКСНЫХ ПРОБЛЕМ СЕРДЕЧНО-СОСУДИСТЫХ ЗАБОЛЕВАНИЙ" Почтовый адрес Российская Федерация, 650002, Кемеровская область - Кузбасс обл, Кемерово г, имени академика Л.С. Барбараша б-р, СТР. 6 Место нахождения Российская Федерация, 650002, Кемеровская область - Кузбасс обл, Кемерово г, имени академика Л.С. Барбараша б-р, СТР. 6 Ответственное должностное лицо Зайцева Ольга Сергеевна Адрес электронной почты torginii@kemcardio.ru Номер контактного телефона 7-3842-345372 Факс Информация отсутствует Дополнительная информация Информация отсутствует Информация о процедуре закупки Дата и время окончания срока подачи заявок 02.09.2026 09:00 Дата проведения процедуры подачи предложений о цене контракта либо о сумме цен единиц товара, работы, услуги 02.09.2026 Дата подведения итогов определения поставщика (подрядчика, исполнителя) 04.09.2026 Условия контракта Начальная (максимальная) цена контракта 3547500.00 РОССИЙСКИЙ РУБЛЬ Информация о сроках исполнения контракта и источниках финансирования Дата начала исполнения контракта 17.09.2026 но не ранее даты заключения контракта Срок исполнения контракта 07.12.2027 Закупка за счет бюджетных средств Нет Закупка за счет собственных средств организации Да Финансовое обеспечение закупки Всего: Оплата за 2026 год Оплата за 2027 год Оплата за 2028 год Сумма на последующие годы 3547500.00 165000.00 3382500.00 0.00 0.00 Этапы исполнения контракта Контракт не разделен на этапы исполнения контракта Финансирование за счет внебюджетных средств Всего: Оплата за 2026 год Оплата за 2027 год Оплата за 2028 год Сумма на последующие годы 3547500.00 165000.00 3382500.00 0.00 0.00 Код видов расходов Код поступления Сумма контракта (в валюте контракта) Всего: на 2026 год на 2027 год на 2028 год Сумма на последующие годы 1 2 3 4 5 6 7 244 3547500.00 165000.00 3382500.00 0.00 0.00 Итого 165000.00 3382500.00 0.00 0.00 Идентификационный код закупки 261420501229042050100104735243250244 Место поставки товара, выполнения работы или оказания услуги Российская Федерация, обл. Кемеровская область - Кузбасс, г.о. Кемеровский, г. Кемерово, б-р имени академика Л.С. Барбараша, стр. 6, Предусмотрена возможность одностороннего отказа от исполнения контракта в соответствии со ст. 95 Закона № 44-ФЗ Да Объект закупки Наименование товара, работы, услуги Код позиции Тип позиции Единица измерения Цена за единицу Количество (объем работы, услуги) Стоимость позиции Комплект ирригационных трубок для системы абляции сердца Идентификатор: 221235221 32.50.13.110-00005862 Товар Штука 16500.00 215.00000000000 3547500.00 Характеристики товара, работы, услуги ( Комплект ирригационных трубок для системы абляции сердца ) Наименование характеристики Значение характеристики Единица измерения характеристики Инструкция по заполнению характеристики в заявке Обоснование включения дополнительной информации в сведения о товаре, работе, услуге Внутренний диаметр иглы 3.4 Миллиметр Значение характеристики не может изменяться участником закупки Высота капельницы ≥ 63 Миллиметр Участник закупки указывает в заявке конкретное значение характеристики Общая длина ≥ 3000 и ≤ 4100 Миллиметр Участник закупки указывает в заявке конкретное значение характеристики 1.Штекерный разъём Люэра наличие Значение характеристики не может изменяться участником закупки • 1.Разъём Люера необходим для фиксации в катетере. • 2.Поставляется в стерильной упаковке для соблюдения медицинских стандартов. • 3. Обеспечение совместимости с оборудованием, состоящим на балансе Заказчика. 2.Стерильность да Значение характеристики не может изменяться участником закупки • 1.Разъём Люера необходим для фиксации в катетере. • 2.Поставляется в стерильной упаковке для соблюдения медицинских стандартов. • 3. Обеспечение совместимости с оборудованием, состоящим на балансе Заказчика. 3.Совместимость трубки совместимы с ирригационным насосом SmartAblate Значение характеристики не может изменяться участником закупки • 1.Разъём Люера необходим для фиксации в катетере. • 2.Поставляется в стерильной упаковке для соблюдения медицинских стандартов. • 3. Обеспечение совместимости с оборудованием, состоящим на балансе Заказчика. Итого: 3547500.00 РОССИЙСКИЙ РУБЛЬ Преимущества и требования к участникам Преимущества Преимущество в соответствии с ч. 3 ст. 30 Закона № 44-ФЗ Требования к участникам 1 Единые требования к участникам закупок в соответствии с ч. 1 ст. 31 Закона № 44-ФЗ 2 Требования к участникам закупок в соответствии с ч. 1.1 ст. 31 Закона № 44-ФЗ 3 Требование об отсутствии в реестре недобросовестных поставщиков (подрядчиков, исполнителей) информации, включенной в такой реестр в связи отказом поставщика (подрядчика, исполнителя) от исполнения контракта по причине введения в отношении заказчика санкций и (или) мер ограничительного характера Применение национального режима по ст. 14 Закона № 44-ФЗ Основанием для установки указания запретов, ограничений закупок товаров, происходящих из иностранных государств, выполняемых работ, оказываемых услуг иностранными лицами, а также преимуществ в отношении товаров российского происхождения, а также товаров происходящих из стран ЕАЭС, выполняемых работ, оказываемых услуг российскими лицами, а также лицами, зарегистрированными в странах ЕАЭС, является Постановление Правительства Российской Федерации о мерах по предоставлению национального режима от 23.12.2024 № 1875. Объект закупки Вид требования Обоснование невозможности соблюдения запрета, ограничения 32.50.13.110</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>5862</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>комплект</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="3" t="n">
+          <t>Комплект ирригационных трубок для системы абляции сердца</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>⌀ иглы 3.4 мм; капельница ≥ 63 мм; длина ≥ 3000 и ≤ 4100 мм</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n">
         <v>3547500</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="8" t="n">
         <v>3547500</v>
       </c>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>НМЦК из обоснования:</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>НМЦК (без НДС):</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
         <v>3547500</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Источник: 852469528.txt</t>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>НМЦК (с НДС):</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>4257000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Источник 1 (НМЦК, цена за ед.): eis_Обоснование НМЦК_unzipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Источник 2 (позиция, кол-во, КТРУ, характеристики): eis_Описание объекта закупки.doc</t>
         </is>
       </c>
     </row>
